--- a/artfynd/A 21876-2026 artfynd.xlsx
+++ b/artfynd/A 21876-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>133670751</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21876-2026 artfynd.xlsx
+++ b/artfynd/A 21876-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133670708</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133670751</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21876-2026 artfynd.xlsx
+++ b/artfynd/A 21876-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133670708</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133670751</v>
       </c>
       <c r="B3" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21876-2026 artfynd.xlsx
+++ b/artfynd/A 21876-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>133670751</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21876-2026 artfynd.xlsx
+++ b/artfynd/A 21876-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>133670751</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21876-2026 artfynd.xlsx
+++ b/artfynd/A 21876-2026 artfynd.xlsx
@@ -790,11 +790,11 @@
         <v>133670751</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
